--- a/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
@@ -75,72 +75,56 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
-  </x:numFmts>
-  <x:fonts count="1">
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,7 +514,6 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
-      <x:c r="A3" s="1"/>
       <x:c r="C3" s="0">
         <x:v>4</x:v>
       </x:c>
@@ -575,7 +558,6 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
-      <x:c r="A4" s="1"/>
       <x:c r="C4" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -667,7 +649,6 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
-      <x:c r="A6" s="1"/>
       <x:c r="C6" s="0">
         <x:v>8</x:v>
       </x:c>
@@ -712,7 +693,6 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
-      <x:c r="A7" s="1"/>
       <x:c r="C7" s="0">
         <x:v>10</x:v>
       </x:c>
@@ -804,7 +784,6 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
-      <x:c r="A9" s="1"/>
       <x:c r="C9" s="0">
         <x:v>13</x:v>
       </x:c>
@@ -849,7 +828,6 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
-      <x:c r="A10" s="1"/>
       <x:c r="C10" s="0">
         <x:v>14</x:v>
       </x:c>
@@ -941,7 +919,6 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
-      <x:c r="A12" s="1"/>
       <x:c r="C12" s="0">
         <x:v>17</x:v>
       </x:c>
@@ -986,7 +963,6 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
-      <x:c r="A13" s="1"/>
       <x:c r="C13" s="0">
         <x:v>18</x:v>
       </x:c>
@@ -1078,7 +1054,6 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
-      <x:c r="A15" s="1"/>
       <x:c r="C15" s="0">
         <x:v>21</x:v>
       </x:c>
@@ -1123,7 +1098,6 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
-      <x:c r="A16" s="1"/>
       <x:c r="C16" s="0">
         <x:v>23</x:v>
       </x:c>
@@ -1215,7 +1189,6 @@
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
-      <x:c r="A18" s="1"/>
       <x:c r="C18" s="0">
         <x:v>25</x:v>
       </x:c>
@@ -1260,7 +1233,6 @@
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
-      <x:c r="A19" s="1"/>
       <x:c r="C19" s="0">
         <x:v>27</x:v>
       </x:c>

--- a/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
@@ -106,7 +106,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0"/>

--- a/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Sparklines/SampleSparklines.xlsx
@@ -1548,7 +1548,6 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
-      <x:c r="A3" s="1"/>
       <x:c r="C3" s="0">
         <x:v>4</x:v>
       </x:c>
@@ -1593,7 +1592,6 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
-      <x:c r="A4" s="1"/>
       <x:c r="C4" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -1685,7 +1683,6 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
-      <x:c r="A6" s="1"/>
       <x:c r="C6" s="0">
         <x:v>8</x:v>
       </x:c>
@@ -1730,7 +1727,6 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
-      <x:c r="A7" s="1"/>
       <x:c r="C7" s="0">
         <x:v>10</x:v>
       </x:c>
@@ -1822,7 +1818,6 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
-      <x:c r="A9" s="1"/>
       <x:c r="C9" s="0">
         <x:v>13</x:v>
       </x:c>
@@ -1867,7 +1862,6 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
-      <x:c r="A10" s="1"/>
       <x:c r="C10" s="0">
         <x:v>14</x:v>
       </x:c>
@@ -1959,7 +1953,6 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
-      <x:c r="A12" s="1"/>
       <x:c r="C12" s="0">
         <x:v>17</x:v>
       </x:c>
@@ -2004,7 +1997,6 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
-      <x:c r="A13" s="1"/>
       <x:c r="C13" s="0">
         <x:v>18</x:v>
       </x:c>
@@ -2096,7 +2088,6 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
-      <x:c r="A15" s="1"/>
       <x:c r="C15" s="0">
         <x:v>21</x:v>
       </x:c>
@@ -2141,7 +2132,6 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
-      <x:c r="A16" s="1"/>
       <x:c r="C16" s="0">
         <x:v>23</x:v>
       </x:c>
@@ -2233,7 +2223,6 @@
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
-      <x:c r="A18" s="1"/>
       <x:c r="C18" s="0">
         <x:v>25</x:v>
       </x:c>
@@ -2278,7 +2267,6 @@
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
-      <x:c r="A19" s="1"/>
       <x:c r="C19" s="0">
         <x:v>27</x:v>
       </x:c>
@@ -2601,7 +2589,6 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
-      <x:c r="A3" s="1"/>
       <x:c r="C3" s="0">
         <x:v>4</x:v>
       </x:c>
@@ -2646,7 +2633,6 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
-      <x:c r="A4" s="1"/>
       <x:c r="C4" s="0">
         <x:v>6</x:v>
       </x:c>
@@ -2738,7 +2724,6 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
-      <x:c r="A6" s="1"/>
       <x:c r="C6" s="0">
         <x:v>8</x:v>
       </x:c>
@@ -2783,7 +2768,6 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
-      <x:c r="A7" s="1"/>
       <x:c r="C7" s="0">
         <x:v>10</x:v>
       </x:c>
@@ -2875,7 +2859,6 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
-      <x:c r="A9" s="1"/>
       <x:c r="C9" s="0">
         <x:v>13</x:v>
       </x:c>
@@ -2920,7 +2903,6 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
-      <x:c r="A10" s="1"/>
       <x:c r="C10" s="0">
         <x:v>14</x:v>
       </x:c>
@@ -3012,7 +2994,6 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
-      <x:c r="A12" s="1"/>
       <x:c r="C12" s="0">
         <x:v>17</x:v>
       </x:c>
@@ -3057,7 +3038,6 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
-      <x:c r="A13" s="1"/>
       <x:c r="C13" s="0">
         <x:v>18</x:v>
       </x:c>
@@ -3149,7 +3129,6 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
-      <x:c r="A15" s="1"/>
       <x:c r="C15" s="0">
         <x:v>21</x:v>
       </x:c>
@@ -3194,7 +3173,6 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
-      <x:c r="A16" s="1"/>
       <x:c r="C16" s="0">
         <x:v>23</x:v>
       </x:c>
@@ -3286,7 +3264,6 @@
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
-      <x:c r="A18" s="1"/>
       <x:c r="C18" s="0">
         <x:v>25</x:v>
       </x:c>
@@ -3331,7 +3308,6 @@
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
-      <x:c r="A19" s="1"/>
       <x:c r="C19" s="0">
         <x:v>27</x:v>
       </x:c>
